--- a/vt_vervestacks_NZL_v1.xlsx
+++ b/vt_vervestacks_NZL_v1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83E06EF9-0126-4468-A08B-8FF9A9FEDAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178B38CD-D8CA-4F76-A74A-99FA6AB041E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{16BB6A0B-CA1A-4643-A595-7B47B2AFB646}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="2" xr2:uid="{16BB6A0B-CA1A-4643-A595-7B47B2AFB646}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="existing_stock" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">existing_stock!$B$10:$L$139</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -6300,6 +6303,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB55E4C3-B83F-4E11-BD59-9819D1821C6C}">
   <dimension ref="B9:T139"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="34.1328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
@@ -7456,7 +7462,7 @@
         <v>143</v>
       </c>
       <c r="J32">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K32">
         <v>50</v>
@@ -7509,7 +7515,7 @@
         <v>143</v>
       </c>
       <c r="J33">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K33">
         <v>55</v>
@@ -7562,7 +7568,7 @@
         <v>143</v>
       </c>
       <c r="J34">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K34">
         <v>50</v>
@@ -7615,7 +7621,7 @@
         <v>169</v>
       </c>
       <c r="J35">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K35">
         <v>50</v>
@@ -7668,7 +7674,7 @@
         <v>169</v>
       </c>
       <c r="J36">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K36">
         <v>50</v>
@@ -7721,7 +7727,7 @@
         <v>143</v>
       </c>
       <c r="J37">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K37">
         <v>66</v>
@@ -7774,7 +7780,7 @@
         <v>169</v>
       </c>
       <c r="J38">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K38">
         <v>58</v>
@@ -7827,7 +7833,7 @@
         <v>169</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K39">
         <v>55</v>
@@ -7880,7 +7886,7 @@
         <v>143</v>
       </c>
       <c r="J40">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K40">
         <v>50</v>
@@ -7933,7 +7939,7 @@
         <v>143</v>
       </c>
       <c r="J41">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K41">
         <v>50</v>
@@ -7986,7 +7992,7 @@
         <v>143</v>
       </c>
       <c r="J42">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K42">
         <v>50</v>
@@ -8039,7 +8045,7 @@
         <v>169</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K43">
         <v>73</v>
@@ -8092,7 +8098,7 @@
         <v>169</v>
       </c>
       <c r="J44">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K44">
         <v>73</v>
@@ -8145,7 +8151,7 @@
         <v>169</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K45">
         <v>73</v>
@@ -8198,7 +8204,7 @@
         <v>169</v>
       </c>
       <c r="J46">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K46">
         <v>50</v>
@@ -8251,7 +8257,7 @@
         <v>169</v>
       </c>
       <c r="J47">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K47">
         <v>50</v>
@@ -8304,7 +8310,7 @@
         <v>169</v>
       </c>
       <c r="J48">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K48">
         <v>50</v>
@@ -8357,7 +8363,7 @@
         <v>169</v>
       </c>
       <c r="J49">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K49">
         <v>50</v>
@@ -8410,7 +8416,7 @@
         <v>169</v>
       </c>
       <c r="J50">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K50">
         <v>50</v>
@@ -8463,7 +8469,7 @@
         <v>169</v>
       </c>
       <c r="J51">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K51">
         <v>50</v>
@@ -8516,7 +8522,7 @@
         <v>143</v>
       </c>
       <c r="J52">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K52">
         <v>50</v>
@@ -8569,7 +8575,7 @@
         <v>169</v>
       </c>
       <c r="J53">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K53">
         <v>50</v>
@@ -8622,7 +8628,7 @@
         <v>169</v>
       </c>
       <c r="J54">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K54">
         <v>50</v>
@@ -8675,7 +8681,7 @@
         <v>169</v>
       </c>
       <c r="J55">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K55">
         <v>50</v>
@@ -8728,7 +8734,7 @@
         <v>169</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -8781,7 +8787,7 @@
         <v>169</v>
       </c>
       <c r="J57">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K57">
         <v>50</v>
@@ -8834,7 +8840,7 @@
         <v>169</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K58">
         <v>50</v>
@@ -8887,7 +8893,7 @@
         <v>143</v>
       </c>
       <c r="J59">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K59">
         <v>73</v>
@@ -8940,7 +8946,7 @@
         <v>169</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K60">
         <v>66</v>
@@ -8993,7 +8999,7 @@
         <v>169</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K61">
         <v>50</v>
@@ -9046,7 +9052,7 @@
         <v>169</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="K62">
         <v>59</v>
